--- a/giro_da_praça_ofertas - SABADO.xlsx
+++ b/giro_da_praça_ofertas - SABADO.xlsx
@@ -1,31 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workflow\automacao_giro_ofertas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F7CA3C3-FF93-4972-9DC7-350869754F9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{103AED9D-66CD-45AD-9421-70CA25985B49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ofertas Finais" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="35">
   <si>
     <t>NOME_PROMOÇÃO</t>
   </si>
@@ -45,15 +40,18 @@
     <t>PROMOÇÃO</t>
   </si>
   <si>
+    <t>SABADO - OFERTAS ESPECIAIS 27/12/25</t>
+  </si>
+  <si>
+    <t>#01 MERCEARIA - #01 CEREAIS E GRÃOS</t>
+  </si>
+  <si>
+    <t>ARROZ BREJEIRO PCT 5KG TIPO 1 BRANCO</t>
+  </si>
+  <si>
     <t>SABADO - BIRITÃO 27/12/25</t>
   </si>
   <si>
-    <t>#05 BEBIDA - #00 ENERGÉTICOS</t>
-  </si>
-  <si>
-    <t>ENERGETICO RED BULL 250ML TRADICIONAL</t>
-  </si>
-  <si>
     <t>#05 BEBIDA - CERVEJAS CX</t>
   </si>
   <si>
@@ -61,12 +59,6 @@
   </si>
   <si>
     <t xml:space="preserve">CERVEJA SKOL 15 X 269ML PILSEN </t>
-  </si>
-  <si>
-    <t>#05 BEBIDA - DESTILADOS</t>
-  </si>
-  <si>
-    <t>CAMPARI 998ML</t>
   </si>
   <si>
     <t>#05 BEBIDA - FERMENTADOS</t>
@@ -142,7 +134,7 @@
   <numFmts count="1">
     <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -162,21 +154,31 @@
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="9"/>
+      <b/>
+      <sz val="16"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
-      <sz val="9"/>
+      <sz val="16"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
+      <sz val="16"/>
+      <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -220,7 +222,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -228,22 +230,32 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -546,400 +558,389 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:F22"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="35.25" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="34.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="23" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.7109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.28515625" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="27.5703125" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="12.28515625" style="8" customWidth="1"/>
+    <col min="4" max="4" width="53.85546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="39.85546875" style="12" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.5703125" style="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="3">
-        <v>102282</v>
-      </c>
-      <c r="D2" s="4" t="s">
+      <c r="C2" s="5">
+        <v>100038</v>
+      </c>
+      <c r="D2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="5"/>
+      <c r="E2" s="11"/>
       <c r="F2" s="7">
-        <v>8.89</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="2" t="s">
+        <v>21.99</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="3">
+      <c r="B4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="5">
         <v>258895</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D4" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="11"/>
+      <c r="F4" s="7">
+        <v>3.69</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="5"/>
-      <c r="F3" s="7">
-        <v>3.69</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="2" t="s">
+      <c r="C5" s="5">
+        <v>324556</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" s="11"/>
+      <c r="F5" s="7">
+        <v>2.79</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="3">
-        <v>324556</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" s="5"/>
-      <c r="F4" s="7">
-        <v>2.79</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" s="3">
-        <v>301843</v>
-      </c>
-      <c r="D5" s="4" t="s">
+      <c r="B6" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="5"/>
-      <c r="F5" s="7">
-        <v>76.989999999999995</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="5">
+        <v>297481</v>
+      </c>
+      <c r="D6" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="3">
-        <v>297481</v>
-      </c>
-      <c r="D6" s="4" t="s">
+      <c r="E6" s="11" t="s">
         <v>15</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>16</v>
       </c>
       <c r="F6" s="7">
         <v>11.99</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7" s="3">
+        <v>13</v>
+      </c>
+      <c r="C7" s="5">
         <v>102036</v>
       </c>
-      <c r="D7" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E7" s="5"/>
+      <c r="D7" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E7" s="11"/>
       <c r="F7" s="7">
         <v>24.99</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C8" s="3">
+        <v>13</v>
+      </c>
+      <c r="C8" s="5">
         <v>139964</v>
       </c>
-      <c r="D8" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E8" s="5"/>
+      <c r="D8" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E8" s="11"/>
       <c r="F8" s="7">
         <v>30.99</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="C10" s="5">
+        <v>105450</v>
+      </c>
+      <c r="D10" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="3">
-        <v>105450</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E10" s="5"/>
+      <c r="E10" s="11"/>
       <c r="F10" s="7">
         <v>38.99</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C11" s="3">
+      <c r="C11" s="5">
         <v>105461</v>
       </c>
-      <c r="D11" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E11" s="5"/>
+      <c r="D11" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E11" s="11"/>
       <c r="F11" s="7">
         <v>33.99</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C12" s="3">
+      <c r="C12" s="5">
         <v>239334</v>
       </c>
-      <c r="D12" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="E12" s="5"/>
+      <c r="D12" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E12" s="11"/>
       <c r="F12" s="7">
         <v>28.99</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C13" s="3">
+      <c r="C13" s="5">
         <v>105456</v>
       </c>
-      <c r="D13" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="E13" s="5"/>
+      <c r="D13" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E13" s="11"/>
       <c r="F13" s="7">
         <v>28.99</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C14" s="3">
+      <c r="C14" s="5">
         <v>105468</v>
       </c>
-      <c r="D14" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="E14" s="5"/>
+      <c r="D14" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E14" s="11"/>
       <c r="F14" s="7">
         <v>18.989999999999998</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C15" s="3">
+      <c r="C15" s="5">
         <v>105471</v>
       </c>
-      <c r="D15" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E15" s="5"/>
+      <c r="D15" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E15" s="11"/>
       <c r="F15" s="7">
         <v>16.989999999999998</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C16" s="3">
+      <c r="C16" s="5">
         <v>105449</v>
       </c>
-      <c r="D16" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="E16" s="5"/>
+      <c r="D16" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E16" s="11"/>
       <c r="F16" s="7">
         <v>34.99</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C17" s="3">
+      <c r="C17" s="5">
         <v>105452</v>
       </c>
-      <c r="D17" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E17" s="5"/>
+      <c r="D17" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="E17" s="11"/>
       <c r="F17" s="7">
         <v>36.99</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B18" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C18" s="5">
+        <v>106053</v>
+      </c>
+      <c r="D18" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C18" s="3">
-        <v>106053</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E18" s="5"/>
+      <c r="E18" s="11"/>
       <c r="F18" s="7">
         <v>18.989999999999998</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C19" s="3">
+        <v>28</v>
+      </c>
+      <c r="C19" s="5">
         <v>105062</v>
       </c>
-      <c r="D19" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="E19" s="5"/>
+      <c r="D19" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="E19" s="11"/>
       <c r="F19" s="7">
         <v>18.989999999999998</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C20" s="3">
+        <v>28</v>
+      </c>
+      <c r="C20" s="5">
         <v>106008</v>
       </c>
-      <c r="D20" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="E20" s="5"/>
+      <c r="D20" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="E20" s="11"/>
       <c r="F20" s="7">
         <v>16.989999999999998</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C21" s="3">
+        <v>28</v>
+      </c>
+      <c r="C21" s="5">
         <v>106034</v>
       </c>
-      <c r="D21" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="E21" s="5"/>
+      <c r="D21" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="E21" s="11"/>
       <c r="F21" s="7">
         <v>10.99</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B22" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C22" s="5">
+        <v>305039</v>
+      </c>
+      <c r="D22" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="C22" s="3">
-        <v>305039</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E22" s="5"/>
+      <c r="E22" s="11"/>
       <c r="F22" s="7">
         <v>18.989999999999998</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.74803149606299213" right="0.74803149606299213" top="0.98425196850393704" bottom="0.98425196850393704" header="0.51181102362204722" footer="0.51181102362204722"/>
+  <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <headerFooter>
+    <oddHeader>&amp;LGIRO DA PRAÇA - SABADO&amp;C&amp;P - &amp;N</oddHeader>
+  </headerFooter>
 </worksheet>
 </file>
--- a/giro_da_praça_ofertas - SABADO.xlsx
+++ b/giro_da_praça_ofertas - SABADO.xlsx
@@ -1,75 +1,149 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workflow\automacao_giro_ofertas\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{760C1833-928A-4140-AB9B-6750BDFB8CD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Ofertas Finais" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Ofertas Finais" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="19">
+  <si>
+    <t>NOME_PROMOÇÃO</t>
+  </si>
+  <si>
+    <t>SESSÃO</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>PRODUTO</t>
+  </si>
+  <si>
+    <t>TIPO</t>
+  </si>
+  <si>
+    <t>PROMOÇÃO</t>
+  </si>
+  <si>
+    <t>SABADO - AÇOUGUE 14/02/26</t>
+  </si>
+  <si>
+    <t>#06 AÇOUGUE - #02 BOVINA</t>
+  </si>
+  <si>
+    <t>ACEM BOVINO COM OSSO KG</t>
+  </si>
+  <si>
+    <t>ALCATRA BOVINA KG</t>
+  </si>
+  <si>
+    <t>CAPA DO CONTRA FILE KG</t>
+  </si>
+  <si>
+    <t>CHAMBARI KG</t>
+  </si>
+  <si>
+    <t>CONTRA FILÉ KG</t>
+  </si>
+  <si>
+    <t>COSTELA BOVINA KG</t>
+  </si>
+  <si>
+    <t>FRALDINHA BOVINA KG</t>
+  </si>
+  <si>
+    <t>#06 AÇOUGUE - #03 SUÍNA</t>
+  </si>
+  <si>
+    <t>BISTECA SUINA DO PERNIL KG</t>
+  </si>
+  <si>
+    <t>PELE SUINA KG</t>
+  </si>
+  <si>
+    <t>TOUCINHO FRESCO KG</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="R$ #,##0.00"/>
+    <numFmt numFmtId="164" formatCode="\R\$\ #,##0.00"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
     </font>
     <font>
+      <sz val="7"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="9"/>
     </font>
     <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <color rgb="00000000"/>
-      <sz val="7"/>
+      <family val="2"/>
     </font>
     <font>
+      <sz val="16"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <color rgb="00000000"/>
-      <sz val="9"/>
+      <family val="2"/>
     </font>
     <font>
+      <i/>
+      <sz val="16"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <i val="1"/>
-      <color rgb="00000000"/>
-      <sz val="9"/>
+      <family val="2"/>
     </font>
     <font>
+      <sz val="16"/>
+      <color theme="1"/>
       <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="10"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -82,108 +156,62 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="9">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -471,295 +499,223 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="36.75" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col min="1" max="1" width="19.7109375" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="19" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="10.7109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="38.85546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.140625" style="8" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.7109375" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>NOME_PROMOÇÃO</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>SESSÃO</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>PRODUTO</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>TIPO</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>PROMOÇÃO</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>SABADO - AÇOUGUE 14/02/26</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>#06 AÇOUGUE - #02 BOVINA</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="n">
+    <row r="1" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="4">
         <v>157014</v>
       </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>ACEM BOVINO COM OSSO KG</t>
-        </is>
-      </c>
-      <c r="E2" s="5" t="inlineStr"/>
-      <c r="F2" s="6" t="n">
+      <c r="D2" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="6"/>
+      <c r="F2" s="7">
         <v>13.99</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>SABADO - AÇOUGUE 14/02/26</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>#06 AÇOUGUE - #02 BOVINA</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="n">
+    <row r="3" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="4">
         <v>105450</v>
       </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>ALCATRA BOVINA KG</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="inlineStr"/>
-      <c r="F3" s="6" t="n">
+      <c r="D3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="6"/>
+      <c r="F3" s="7">
         <v>41.99</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>SABADO - AÇOUGUE 14/02/26</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>#06 AÇOUGUE - #02 BOVINA</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="n">
+    <row r="4" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="4">
         <v>239334</v>
       </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>CAPA DO CONTRA FILE KG</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="inlineStr"/>
-      <c r="F4" s="6" t="n">
+      <c r="D4" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="6"/>
+      <c r="F4" s="7">
         <v>28.99</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>SABADO - AÇOUGUE 14/02/26</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>#06 AÇOUGUE - #02 BOVINA</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="n">
+    <row r="5" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="4">
         <v>105458</v>
       </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>CHAMBARI KG</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr"/>
-      <c r="F5" s="6" t="n">
-        <v>18.99</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>SABADO - AÇOUGUE 14/02/26</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>#06 AÇOUGUE - #02 BOVINA</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="n">
+      <c r="D5" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="6"/>
+      <c r="F5" s="7">
+        <v>18.989999999999998</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="4">
         <v>105451</v>
       </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>CONTRA FILÉ KG</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr"/>
-      <c r="F6" s="6" t="n">
+      <c r="D6" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" s="6"/>
+      <c r="F6" s="7">
         <v>39.99</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>SABADO - AÇOUGUE 14/02/26</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>#06 AÇOUGUE - #02 BOVINA</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="n">
+    <row r="7" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="4">
         <v>105471</v>
       </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>COSTELA BOVINA KG</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr"/>
-      <c r="F7" s="6" t="n">
-        <v>18.99</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>SABADO - AÇOUGUE 14/02/26</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>#06 AÇOUGUE - #02 BOVINA</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="n">
+      <c r="D7" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="6"/>
+      <c r="F7" s="7">
+        <v>18.989999999999998</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="4">
         <v>105474</v>
       </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>FRALDINHA BOVINA KG</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="inlineStr"/>
-      <c r="F8" s="6" t="n">
+      <c r="D8" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E8" s="6"/>
+      <c r="F8" s="7">
         <v>34.99</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>SABADO - AÇOUGUE 14/02/26</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>#06 AÇOUGUE - #03 SUÍNA</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="n">
+    <row r="9" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" s="4">
         <v>105062</v>
       </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>BISTECA SUINA DO PERNIL KG</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr"/>
-      <c r="F9" s="6" t="n">
-        <v>17.99</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>SABADO - AÇOUGUE 14/02/26</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>#06 AÇOUGUE - #03 SUÍNA</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="n">
+      <c r="D9" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E9" s="6"/>
+      <c r="F9" s="7">
+        <v>17.989999999999998</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" s="4">
         <v>106052</v>
       </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>PELE SUINA KG</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="inlineStr"/>
-      <c r="F10" s="6" t="n">
+      <c r="D10" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E10" s="6"/>
+      <c r="F10" s="7">
         <v>12.99</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>SABADO - AÇOUGUE 14/02/26</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>#06 AÇOUGUE - #03 SUÍNA</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="n">
+    <row r="11" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" s="4">
         <v>106032</v>
       </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>TOUCINHO FRESCO KG</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr"/>
-      <c r="F11" s="6" t="n">
-        <v>18.99</v>
+      <c r="D11" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E11" s="6"/>
+      <c r="F11" s="7">
+        <v>18.989999999999998</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.74803149606299213" right="0.74803149606299213" top="0.98425196850393704" bottom="0.98425196850393704" header="0.51181102362204722" footer="0.51181102362204722"/>
+  <pageSetup paperSize="9" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <headerFooter>
+    <oddHeader>&amp;LGIRO DA PRAÇA - SABADO&amp;C&amp;P - &amp;N</oddHeader>
+  </headerFooter>
 </worksheet>
 </file>
--- a/giro_da_praça_ofertas - SABADO.xlsx
+++ b/giro_da_praça_ofertas - SABADO.xlsx
@@ -1,26 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workflow\automacao_giro_ofertas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA11172C-773E-4EFE-ADAB-4FBBC5C087B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{965E38DC-CF7F-4AC1-88C6-4B80C414837D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="5745" yWindow="3855" windowWidth="16200" windowHeight="9270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ofertas Finais" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
@@ -33,9 +28,6 @@
     <t>SESSÃO</t>
   </si>
   <si>
-    <t>ID</t>
-  </si>
-  <si>
     <t>PRODUTO</t>
   </si>
   <si>
@@ -160,6 +152,9 @@
   </si>
   <si>
     <t xml:space="preserve">OVOS DE GRANJA IANA BDJ 30UN BRANCOS </t>
+  </si>
+  <si>
+    <t>P</t>
   </si>
 </sst>
 </file>
@@ -169,7 +164,7 @@
   <numFmts count="1">
     <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -182,24 +177,35 @@
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="7"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
-      <sz val="9"/>
-      <color rgb="FFFFFFFF"/>
+      <sz val="16"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
-      <sz val="10"/>
+      <sz val="16"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -249,7 +255,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -257,19 +263,23 @@
     <xf numFmtId="49" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -576,563 +586,563 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F32"/>
-  <sheetFormatPr defaultRowHeight="28.5" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="21" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="32" customWidth="1"/>
-    <col min="2" max="2" width="41" customWidth="1"/>
-    <col min="3" max="3" width="10" customWidth="1"/>
-    <col min="4" max="4" width="41" customWidth="1"/>
-    <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="6" max="6" width="10.7109375" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.140625" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="36.140625" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="10.7109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="59.28515625" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.7109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.5703125" style="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="B2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="5">
+        <v>105840</v>
+      </c>
+      <c r="D2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="3">
-        <v>105840</v>
-      </c>
-      <c r="D2" s="4" t="s">
+      <c r="E2" s="6"/>
+      <c r="F2" s="7">
+        <v>14.99</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="4"/>
-      <c r="F2" s="6">
+      <c r="C3" s="5">
+        <v>105461</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="6"/>
+      <c r="F3" s="7">
+        <v>33.99</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="5">
+        <v>152232</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="6"/>
+      <c r="F4" s="7">
+        <v>12.99</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="5">
+        <v>322584</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="6"/>
+      <c r="F5" s="7">
+        <v>38.99</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="5">
+        <v>105451</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" s="6"/>
+      <c r="F6" s="7">
+        <v>39.99</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="5">
+        <v>105471</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="6"/>
+      <c r="F7" s="7">
+        <v>19.989999999999998</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="5">
+        <v>105449</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E8" s="6"/>
+      <c r="F8" s="7">
+        <v>34.99</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="5">
+        <v>105435</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="E9" s="6"/>
+      <c r="F9" s="7">
+        <v>39.99</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="5">
+        <v>105453</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E10" s="6"/>
+      <c r="F10" s="7">
+        <v>45.99</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="5">
+        <v>107260</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E11" s="6"/>
+      <c r="F11" s="7">
+        <v>32.99</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C13" s="5">
+        <v>105023</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E13" s="6"/>
+      <c r="F13" s="7">
+        <v>5.99</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14" s="5">
+        <v>104931</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E14" s="6"/>
+      <c r="F14" s="7">
+        <v>7.99</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C15" s="5">
+        <v>104855</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E15" s="6"/>
+      <c r="F15" s="7">
+        <v>4.3899999999999997</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C16" s="5">
+        <v>104881</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E16" s="6"/>
+      <c r="F16" s="7">
+        <v>8.99</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C17" s="5">
+        <v>104928</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E17" s="6"/>
+      <c r="F17" s="7">
+        <v>6.99</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C18" s="5">
+        <v>104883</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E18" s="6"/>
+      <c r="F18" s="7">
+        <v>6.99</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C19" s="5">
+        <v>108982</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E19" s="6"/>
+      <c r="F19" s="7">
+        <v>12.99</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C20" s="5">
+        <v>104944</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="E20" s="6"/>
+      <c r="F20" s="7">
         <v>14.99</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="3">
-        <v>105461</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" s="4"/>
-      <c r="F3" s="6">
-        <v>33.99</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="3">
-        <v>152232</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" s="4"/>
-      <c r="F4" s="6">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C21" s="5">
+        <v>104947</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E21" s="6"/>
+      <c r="F21" s="7">
+        <v>2.19</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C22" s="5">
+        <v>104996</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="E22" s="6"/>
+      <c r="F22" s="7">
+        <v>6.99</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C23" s="5">
+        <v>105010</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="E23" s="6"/>
+      <c r="F23" s="7">
+        <v>5.99</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C24" s="5">
+        <v>105001</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="E24" s="6"/>
+      <c r="F24" s="7">
+        <v>6.99</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C25" s="5">
+        <v>104862</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="E25" s="6"/>
+      <c r="F25" s="7">
+        <v>5.59</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C26" s="5">
+        <v>104961</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="E26" s="6"/>
+      <c r="F26" s="7">
+        <v>8.99</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C27" s="5">
+        <v>104937</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="E27" s="6"/>
+      <c r="F27" s="7">
+        <v>19.989999999999998</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C28" s="5">
+        <v>104919</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="E28" s="6"/>
+      <c r="F28" s="7">
+        <v>3.69</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C29" s="5">
+        <v>104992</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E29" s="6"/>
+      <c r="F29" s="7">
+        <v>4.99</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C31" s="5">
+        <v>331438</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="E31" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="F31" s="7">
         <v>12.99</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" s="3">
-        <v>322584</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E5" s="4"/>
-      <c r="F5" s="6">
-        <v>38.99</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" s="3">
-        <v>105451</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E6" s="4"/>
-      <c r="F6" s="6">
-        <v>39.99</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="3">
-        <v>105471</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E7" s="4"/>
-      <c r="F7" s="6">
-        <v>19.989999999999998</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="3">
-        <v>105449</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E8" s="4"/>
-      <c r="F8" s="6">
-        <v>34.99</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="3">
-        <v>105435</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="E9" s="4"/>
-      <c r="F9" s="6">
-        <v>39.99</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="3">
-        <v>105453</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E10" s="4"/>
-      <c r="F10" s="6">
-        <v>45.99</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="3">
-        <v>107260</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E11" s="4"/>
-      <c r="F11" s="6">
-        <v>32.99</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C13" s="3">
-        <v>105023</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E13" s="4"/>
-      <c r="F13" s="6">
-        <v>5.99</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C14" s="3">
-        <v>104931</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E14" s="4"/>
-      <c r="F14" s="6">
-        <v>7.99</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C15" s="3">
-        <v>104855</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="E15" s="4"/>
-      <c r="F15" s="6">
-        <v>4.3899999999999997</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C16" s="3">
-        <v>104881</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="E16" s="4"/>
-      <c r="F16" s="6">
-        <v>8.99</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C17" s="3">
-        <v>104928</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="E17" s="4"/>
-      <c r="F17" s="6">
-        <v>6.99</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C18" s="3">
-        <v>104883</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E18" s="4"/>
-      <c r="F18" s="6">
-        <v>6.99</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C19" s="3">
-        <v>108982</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="E19" s="4"/>
-      <c r="F19" s="6">
-        <v>12.99</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C20" s="3">
-        <v>104944</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E20" s="4"/>
-      <c r="F20" s="6">
-        <v>14.99</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C21" s="3">
-        <v>104947</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="E21" s="4"/>
-      <c r="F21" s="6">
-        <v>2.19</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C22" s="3">
-        <v>104996</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E22" s="4"/>
-      <c r="F22" s="6">
-        <v>6.99</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C23" s="3">
-        <v>105010</v>
-      </c>
-      <c r="D23" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="E23" s="4"/>
-      <c r="F23" s="6">
-        <v>5.99</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C24" s="3">
-        <v>105001</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="E24" s="4"/>
-      <c r="F24" s="6">
-        <v>6.99</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C25" s="3">
-        <v>104862</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="E25" s="4"/>
-      <c r="F25" s="6">
-        <v>5.59</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C26" s="3">
-        <v>104961</v>
-      </c>
-      <c r="D26" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E26" s="4"/>
-      <c r="F26" s="6">
-        <v>8.99</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C27" s="3">
-        <v>104937</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="E27" s="4"/>
-      <c r="F27" s="6">
-        <v>19.989999999999998</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C28" s="3">
-        <v>104919</v>
-      </c>
-      <c r="D28" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="E28" s="4"/>
-      <c r="F28" s="6">
-        <v>3.69</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C29" s="3">
-        <v>104992</v>
-      </c>
-      <c r="D29" s="4" t="s">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B32" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="E29" s="4"/>
-      <c r="F29" s="6">
-        <v>4.99</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C31" s="3">
-        <v>331438</v>
-      </c>
-      <c r="D31" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="E31" s="4" t="s">
+      <c r="C32" s="5">
+        <v>328966</v>
+      </c>
+      <c r="D32" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="F31" s="6">
-        <v>12.99</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C32" s="3">
-        <v>328966</v>
-      </c>
-      <c r="D32" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="E32" s="4"/>
-      <c r="F32" s="6">
+      <c r="E32" s="6"/>
+      <c r="F32" s="7">
         <v>17.989999999999998</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.74803149606299213" right="0.74803149606299213" top="0.98425196850393704" bottom="0.98425196850393704" header="0.51181102362204722" footer="0.51181102362204722"/>
-  <pageSetup paperSize="9" scale="89" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" r:id="rId1"/>
   <headerFooter>
     <oddHeader>&amp;LGIRO DA PRAÇA - SABADO
 &amp;C&amp;P - &amp;N</oddHeader>

--- a/giro_da_praça_ofertas - SABADO.xlsx
+++ b/giro_da_praça_ofertas - SABADO.xlsx
@@ -1,40 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workflow\automacao_giro_ofertas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{975E1997-82AC-4A20-94E7-19CE677ABF7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A274AEA-D428-49E1-8861-A1038D722EDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ofertas Finais" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="47">
   <si>
     <t>NOME_PROMOÇÃO</t>
   </si>
@@ -175,132 +161,6 @@
   </si>
   <si>
     <t xml:space="preserve">OVOS DE GRANJA IANA BDJ 30UN BRANCOS </t>
-  </si>
-  <si>
-    <t>SABADO/DOMINGO - BIRITÃO 07 E 08/03/26</t>
-  </si>
-  <si>
-    <t>#05 BEBIDA - CERVEJAS</t>
-  </si>
-  <si>
-    <t>CERVEJA SPATEN PURO MALTE LONG NECK 355ML</t>
-  </si>
-  <si>
-    <t>CERVEJA STELLA ARTOIS LONG NECK 330ML</t>
-  </si>
-  <si>
-    <t>CERVEJA TIJUCA 355ML SILVER</t>
-  </si>
-  <si>
-    <t>#05 BEBIDA - CERVEJAS CX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CERVEJA ANTARCTICA ORIGINAL 15 X 269ML </t>
-  </si>
-  <si>
-    <t>#05 BEBIDA - DESTILADOS</t>
-  </si>
-  <si>
-    <t>AGUARDENTE CANINHA SERTANEJA 970ML</t>
-  </si>
-  <si>
-    <t>BEBIDA ALCOOLICA FIU FIU 750ML TANGERINA ACEROLA</t>
-  </si>
-  <si>
-    <t>CACHAÇA BANANAZINHA 900ML</t>
-  </si>
-  <si>
-    <t>CACHAÇA LUA NOVA 600ML</t>
-  </si>
-  <si>
-    <t>CACHAÇA TERRA BRAZILIS 750ML ENVELHECIDA</t>
-  </si>
-  <si>
-    <t>GIN BEEFEATER 750ML</t>
-  </si>
-  <si>
-    <t>RESERVA 51 700ML UNICA</t>
-  </si>
-  <si>
-    <t>VODKA CIROC 750ML</t>
-  </si>
-  <si>
-    <t>VODKA KETEL ONE 1L</t>
-  </si>
-  <si>
-    <t>WHISKY BALLANTINES 1L 10 ANOS</t>
-  </si>
-  <si>
-    <t>WHISKY BLACK &amp; WHITE 1L 8 ANOS</t>
-  </si>
-  <si>
-    <t>WHISKY OLD PARR 1L 12 ANOS</t>
-  </si>
-  <si>
-    <t>WHISKY PASSPORT 1L</t>
-  </si>
-  <si>
-    <t>#05 BEBIDA - FERMENTADOS</t>
-  </si>
-  <si>
-    <t>JURUBEBA LEÃO NORTE 600ML</t>
-  </si>
-  <si>
-    <t>VINHO PERGOLA 1L TINTO SECO</t>
-  </si>
-  <si>
-    <t>VINHO PERGOLA 1L TINTO SUAVE</t>
-  </si>
-  <si>
-    <t>SEXTA/DOMINGO - PERECIVEIS 06 A 08/03/26</t>
-  </si>
-  <si>
-    <t>#02 MERCEARIA - CONGELADOS - CARNES</t>
-  </si>
-  <si>
-    <t>CALDO VERDE SEARA 300G COM CALABRESA</t>
-  </si>
-  <si>
-    <t>#02 MERCEARIA - CONGELADOS - MASSAS</t>
-  </si>
-  <si>
-    <t>PIZZA CONGELADA SEARA 460G FRANGO COM CATUPIRY</t>
-  </si>
-  <si>
-    <t>#02 MERCEARIA - LATICÍNIOS - BEBIDAS LACTEAS</t>
-  </si>
-  <si>
-    <t>BEBIDA LACTEA FRUTILAC BDJ 480G MORANGO</t>
-  </si>
-  <si>
-    <t>IOGURTE DANONE 1250G</t>
-  </si>
-  <si>
-    <t>COCO, MORANGO, VITAMINA DE FRUTAS</t>
-  </si>
-  <si>
-    <t>#02 MERCEARIA - MASSAS</t>
-  </si>
-  <si>
-    <t>MASSA DE PASTEL MEZZANI 500G</t>
-  </si>
-  <si>
-    <t>TAGLIATELLE FRESCO MEZZANI 500G</t>
-  </si>
-  <si>
-    <t>#06 AÇOUGUE - #01 AVES</t>
-  </si>
-  <si>
-    <t>COXA COM SOBRECOXA SADIA 1KG</t>
-  </si>
-  <si>
-    <t>COXA DE FRANGO SADIA BDJ 1KG</t>
-  </si>
-  <si>
-    <t>FRANGO DE PADARIA SEARA 1KG A PASSARINHO</t>
-  </si>
-  <si>
-    <t>MEIO DA ASA DE FRANGO SEARA 1KG TEMPERADA</t>
   </si>
 </sst>
 </file>
@@ -714,17 +574,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F66"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="30.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="34.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="43.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="31.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="34" customWidth="1"/>
+    <col min="2" max="2" width="41" customWidth="1"/>
+    <col min="3" max="3" width="10" customWidth="1"/>
+    <col min="4" max="4" width="41" customWidth="1"/>
+    <col min="5" max="5" width="11" customWidth="1"/>
     <col min="6" max="6" width="10.7109375" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1159,7 +1016,7 @@
       </c>
       <c r="E25" s="5"/>
       <c r="F25" s="7">
-        <v>6.62</v>
+        <v>6.59</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -1290,554 +1147,7 @@
         <v>17.989999999999998</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C35" s="3">
-        <v>259118</v>
-      </c>
-      <c r="D35" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="E35" s="5"/>
-      <c r="F35" s="7">
-        <v>5.99</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C36" s="3">
-        <v>244191</v>
-      </c>
-      <c r="D36" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="E36" s="5"/>
-      <c r="F36" s="7">
-        <v>6.79</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C37" s="3">
-        <v>312159</v>
-      </c>
-      <c r="D37" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="E37" s="5"/>
-      <c r="F37" s="7">
-        <v>6.69</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C38" s="3">
-        <v>287369</v>
-      </c>
-      <c r="D38" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="E38" s="5"/>
-      <c r="F38" s="7">
-        <f>15*3.79</f>
-        <v>56.85</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C39" s="3">
-        <v>193636</v>
-      </c>
-      <c r="D39" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="E39" s="5"/>
-      <c r="F39" s="7">
-        <v>11.99</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C40" s="3">
-        <v>236673</v>
-      </c>
-      <c r="D40" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="E40" s="5"/>
-      <c r="F40" s="7">
-        <v>42.99</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C41" s="3">
-        <v>215568</v>
-      </c>
-      <c r="D41" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="E41" s="5"/>
-      <c r="F41" s="7">
-        <v>36.99</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C42" s="3">
-        <v>157975</v>
-      </c>
-      <c r="D42" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="E42" s="5"/>
-      <c r="F42" s="7">
-        <v>36.99</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C43" s="3">
-        <v>210317</v>
-      </c>
-      <c r="D43" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="E43" s="5"/>
-      <c r="F43" s="7">
-        <v>55.99</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C44" s="3">
-        <v>225711</v>
-      </c>
-      <c r="D44" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="E44" s="5"/>
-      <c r="F44" s="7">
-        <v>115.99</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C45" s="3">
-        <v>210315</v>
-      </c>
-      <c r="D45" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="E45" s="5"/>
-      <c r="F45" s="7">
-        <v>182.99</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C46" s="3">
-        <v>145658</v>
-      </c>
-      <c r="D46" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="E46" s="5"/>
-      <c r="F46" s="7">
-        <v>109.99</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C47" s="3">
-        <v>231000</v>
-      </c>
-      <c r="D47" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="E47" s="5"/>
-      <c r="F47" s="7">
-        <v>159.99</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C48" s="3">
-        <v>334785</v>
-      </c>
-      <c r="D48" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="E48" s="5"/>
-      <c r="F48" s="7">
-        <v>139.99</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C49" s="3">
-        <v>110373</v>
-      </c>
-      <c r="D49" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="E49" s="5"/>
-      <c r="F49" s="7">
-        <v>109.99</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C50" s="3">
-        <v>102077</v>
-      </c>
-      <c r="D50" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="E50" s="5"/>
-      <c r="F50" s="7">
-        <v>179.99</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C51" s="3">
-        <v>102082</v>
-      </c>
-      <c r="D51" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="E51" s="5"/>
-      <c r="F51" s="7">
-        <v>71.989999999999995</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A52" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C52" s="3">
-        <v>102165</v>
-      </c>
-      <c r="D52" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="E52" s="5"/>
-      <c r="F52" s="7">
-        <v>24.99</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A53" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C53" s="3">
-        <v>159832</v>
-      </c>
-      <c r="D53" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="E53" s="5"/>
-      <c r="F53" s="7">
-        <v>31.99</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B54" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C54" s="3">
-        <v>139964</v>
-      </c>
-      <c r="D54" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="E54" s="5"/>
-      <c r="F54" s="7">
-        <v>27.99</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A56" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="B56" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="C56" s="3">
-        <v>320013</v>
-      </c>
-      <c r="D56" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="E56" s="5"/>
-      <c r="F56" s="7">
-        <v>2.99</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A57" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="C57" s="3">
-        <v>130293</v>
-      </c>
-      <c r="D57" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="E57" s="5"/>
-      <c r="F57" s="7">
-        <v>22.99</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A58" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="B58" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="C58" s="3">
-        <v>306946</v>
-      </c>
-      <c r="D58" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="E58" s="5"/>
-      <c r="F58" s="7">
-        <v>4.99</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A59" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="B59" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="C59" s="3">
-        <v>246975</v>
-      </c>
-      <c r="D59" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="E59" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="F59" s="7">
-        <v>21.99</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="B60" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C60" s="3">
-        <v>150940</v>
-      </c>
-      <c r="D60" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="E60" s="5"/>
-      <c r="F60" s="7">
-        <v>13.99</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="B61" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C61" s="3">
-        <v>206159</v>
-      </c>
-      <c r="D61" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="E61" s="5"/>
-      <c r="F61" s="7">
-        <v>15.99</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A63" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="B63" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C63" s="3">
-        <v>111324</v>
-      </c>
-      <c r="D63" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="E63" s="5"/>
-      <c r="F63" s="7">
-        <v>20.99</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A64" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="B64" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C64" s="3">
-        <v>111565</v>
-      </c>
-      <c r="D64" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="E64" s="5"/>
-      <c r="F64" s="7">
-        <v>12.99</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A65" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="B65" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C65" s="3">
-        <v>298984</v>
-      </c>
-      <c r="D65" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="E65" s="5"/>
-      <c r="F65" s="7">
-        <v>13.99</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A66" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="B66" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C66" s="3">
-        <v>320121</v>
-      </c>
-      <c r="D66" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="E66" s="5"/>
-      <c r="F66" s="7">
-        <v>23.99</v>
-      </c>
-    </row>
   </sheetData>
-  <pageMargins left="0.74803149606299213" right="0.74803149606299213" top="0.98425196850393704" bottom="0.98425196850393704" header="0.51181102362204722" footer="0.51181102362204722"/>
-  <pageSetup paperSize="9" scale="83" fitToHeight="0" orientation="landscape" r:id="rId1"/>
-  <headerFooter>
-    <oddHeader>&amp;LGIRO DA PRAÇA - SABADO&amp;C&amp;P - &amp;N</oddHeader>
-  </headerFooter>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/giro_da_praça_ofertas - SABADO.xlsx
+++ b/giro_da_praça_ofertas - SABADO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workflow\automacao_giro_ofertas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A274AEA-D428-49E1-8861-A1038D722EDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F201BC5A-B582-4AA9-95D8-824F2A06AEBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -170,7 +170,7 @@
   <numFmts count="1">
     <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -190,21 +190,31 @@
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="9"/>
+      <b/>
+      <sz val="16"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
-      <sz val="9"/>
+      <sz val="16"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
+      <sz val="16"/>
+      <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -248,7 +258,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -256,22 +266,26 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -574,580 +588,587 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:F33"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="34.5" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="34" customWidth="1"/>
-    <col min="2" max="2" width="41" customWidth="1"/>
-    <col min="3" max="3" width="10" customWidth="1"/>
-    <col min="4" max="4" width="41" customWidth="1"/>
-    <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="6" max="6" width="10.7109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.140625" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="30.42578125" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="10.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="57.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="9" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.5703125" style="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="3">
+      <c r="C2" s="5">
         <v>105461</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="5"/>
-      <c r="F2" s="7">
+      <c r="E2" s="7"/>
+      <c r="F2" s="8">
         <v>33.99</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3" s="5">
         <v>105457</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="5"/>
-      <c r="F3" s="7">
+      <c r="E3" s="7"/>
+      <c r="F3" s="8">
         <v>34.99</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="5">
         <v>105458</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="5"/>
-      <c r="F4" s="7">
+      <c r="E4" s="7"/>
+      <c r="F4" s="8">
         <v>17.989999999999998</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5" s="5">
         <v>105451</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="5"/>
-      <c r="F5" s="7">
+      <c r="E5" s="7"/>
+      <c r="F5" s="8">
         <v>36.99</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C6" s="5">
         <v>105449</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E6" s="5"/>
-      <c r="F6" s="7">
+      <c r="E6" s="7"/>
+      <c r="F6" s="8">
         <v>34.99</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="3">
+      <c r="C7" s="5">
         <v>107260</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E7" s="5"/>
-      <c r="F7" s="7">
+      <c r="E7" s="7"/>
+      <c r="F7" s="8">
         <v>31.99</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C8" s="3">
+      <c r="C8" s="5">
         <v>105062</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E8" s="5"/>
-      <c r="F8" s="7">
+      <c r="E8" s="7"/>
+      <c r="F8" s="8">
         <v>16.989999999999998</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="3">
+      <c r="C9" s="5">
         <v>105433</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="E9" s="5"/>
-      <c r="F9" s="7">
+      <c r="E9" s="7"/>
+      <c r="F9" s="8">
         <v>19.989999999999998</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="3">
+      <c r="C10" s="5">
         <v>106054</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="E10" s="5"/>
-      <c r="F10" s="7">
+      <c r="E10" s="7"/>
+      <c r="F10" s="8">
         <v>19.989999999999998</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="3">
+      <c r="C11" s="5">
         <v>258810</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="E11" s="5"/>
-      <c r="F11" s="7">
+      <c r="E11" s="7"/>
+      <c r="F11" s="8">
         <v>16.989999999999998</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C12" s="3">
+      <c r="C12" s="5">
         <v>305039</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="E12" s="5"/>
-      <c r="F12" s="7">
+      <c r="E12" s="7"/>
+      <c r="F12" s="8">
         <v>19.989999999999998</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C13" s="3">
+      <c r="C13" s="5">
         <v>234676</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="E13" s="5"/>
-      <c r="F13" s="7">
+      <c r="E13" s="7"/>
+      <c r="F13" s="8">
         <v>21.99</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>22</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C15" s="3">
+      <c r="C15" s="5">
         <v>104998</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="E15" s="5"/>
-      <c r="F15" s="7">
+      <c r="E15" s="7"/>
+      <c r="F15" s="8">
         <v>10.99</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>22</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="3">
+      <c r="C16" s="5">
         <v>104905</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="E16" s="5"/>
-      <c r="F16" s="7">
+      <c r="E16" s="7"/>
+      <c r="F16" s="8">
         <v>5.69</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>22</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C17" s="3">
+      <c r="C17" s="5">
         <v>105023</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D17" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E17" s="5"/>
-      <c r="F17" s="7">
+      <c r="E17" s="7"/>
+      <c r="F17" s="8">
         <v>6.39</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>22</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C18" s="3">
+      <c r="C18" s="5">
         <v>104931</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="D18" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="E18" s="5"/>
-      <c r="F18" s="7">
+      <c r="E18" s="7"/>
+      <c r="F18" s="8">
         <v>9.89</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>22</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C19" s="3">
+      <c r="C19" s="5">
         <v>104881</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="D19" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="E19" s="5"/>
-      <c r="F19" s="7">
+      <c r="E19" s="7"/>
+      <c r="F19" s="8">
         <v>6.69</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>22</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C20" s="3">
+      <c r="C20" s="5">
         <v>104928</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D20" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="E20" s="5"/>
-      <c r="F20" s="7">
+      <c r="E20" s="7"/>
+      <c r="F20" s="8">
         <v>7.19</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>22</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C21" s="3">
+      <c r="C21" s="5">
         <v>104944</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="D21" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="E21" s="5"/>
-      <c r="F21" s="7">
+      <c r="E21" s="7"/>
+      <c r="F21" s="8">
         <v>14.99</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>22</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C22" s="3">
+      <c r="C22" s="5">
         <v>104947</v>
       </c>
-      <c r="D22" s="4" t="s">
+      <c r="D22" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="E22" s="5"/>
-      <c r="F22" s="7">
+      <c r="E22" s="7"/>
+      <c r="F22" s="8">
         <v>2.39</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>22</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C23" s="3">
+      <c r="C23" s="5">
         <v>104996</v>
       </c>
-      <c r="D23" s="4" t="s">
+      <c r="D23" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="E23" s="5"/>
-      <c r="F23" s="7">
+      <c r="E23" s="7"/>
+      <c r="F23" s="8">
         <v>6.99</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>22</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C24" s="3">
+      <c r="C24" s="5">
         <v>113290</v>
       </c>
-      <c r="D24" s="4" t="s">
+      <c r="D24" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="E24" s="5"/>
-      <c r="F24" s="7">
+      <c r="E24" s="7"/>
+      <c r="F24" s="8">
         <v>14.99</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>22</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C25" s="3">
+      <c r="C25" s="5">
         <v>105010</v>
       </c>
-      <c r="D25" s="4" t="s">
+      <c r="D25" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E25" s="5"/>
-      <c r="F25" s="7">
+      <c r="E25" s="7"/>
+      <c r="F25" s="8">
         <v>6.59</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>22</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C26" s="3">
+      <c r="C26" s="5">
         <v>105001</v>
       </c>
-      <c r="D26" s="4" t="s">
+      <c r="D26" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="E26" s="5"/>
-      <c r="F26" s="7">
+      <c r="E26" s="7"/>
+      <c r="F26" s="8">
         <v>7.49</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>22</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="3">
+      <c r="C27" s="5">
         <v>104862</v>
       </c>
-      <c r="D27" s="4" t="s">
+      <c r="D27" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="E27" s="5"/>
-      <c r="F27" s="7">
+      <c r="E27" s="7"/>
+      <c r="F27" s="8">
         <v>7.49</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>22</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C28" s="3">
+      <c r="C28" s="5">
         <v>104961</v>
       </c>
-      <c r="D28" s="4" t="s">
+      <c r="D28" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="E28" s="5"/>
-      <c r="F28" s="7">
+      <c r="E28" s="7"/>
+      <c r="F28" s="8">
         <v>10.49</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>22</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C29" s="3">
+      <c r="C29" s="5">
         <v>104937</v>
       </c>
-      <c r="D29" s="4" t="s">
+      <c r="D29" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="E29" s="5"/>
-      <c r="F29" s="7">
+      <c r="E29" s="7"/>
+      <c r="F29" s="8">
         <v>21.99</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>22</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C30" s="3">
+      <c r="C30" s="5">
         <v>104992</v>
       </c>
-      <c r="D30" s="4" t="s">
+      <c r="D30" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="E30" s="5"/>
-      <c r="F30" s="7">
+      <c r="E30" s="7"/>
+      <c r="F30" s="8">
         <v>4.99</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>22</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C32" s="3">
+      <c r="C32" s="5">
         <v>331438</v>
       </c>
-      <c r="D32" s="4" t="s">
+      <c r="D32" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="E32" s="5" t="s">
+      <c r="E32" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="F32" s="7">
+      <c r="F32" s="8">
         <v>12.99</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>22</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C33" s="3">
+      <c r="C33" s="5">
         <v>328966</v>
       </c>
-      <c r="D33" s="4" t="s">
+      <c r="D33" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="E33" s="5"/>
-      <c r="F33" s="7">
+      <c r="E33" s="7"/>
+      <c r="F33" s="8">
         <v>17.989999999999998</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.74803149606299213" right="0.74803149606299213" top="0.98425196850393704" bottom="0.98425196850393704" header="0.51181102362204722" footer="0.51181102362204722"/>
+  <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <headerFooter>
+    <oddHeader>&amp;LGIRO DA PRAÇA - SABADO&amp;C&amp;P - &amp;N</oddHeader>
+  </headerFooter>
 </worksheet>
 </file>
--- a/giro_da_praça_ofertas - SABADO.xlsx
+++ b/giro_da_praça_ofertas - SABADO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workflow\automacao_giro_ofertas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78A024D2-0C4A-450F-B371-915FA8D3DBD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9209079-077B-4948-ADC1-60DF5B7800C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -89,7 +89,7 @@
   <numFmts count="1">
     <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -109,21 +109,31 @@
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="9"/>
+      <b/>
+      <sz val="16"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
-      <sz val="9"/>
+      <sz val="16"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
+      <sz val="16"/>
+      <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -167,7 +177,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -175,22 +185,26 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -493,236 +507,243 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:F12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="33.75" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="29" customWidth="1"/>
-    <col min="2" max="2" width="28" customWidth="1"/>
-    <col min="3" max="3" width="10" customWidth="1"/>
-    <col min="4" max="4" width="36" customWidth="1"/>
-    <col min="5" max="5" width="10" customWidth="1"/>
-    <col min="6" max="6" width="10.7109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.42578125" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="19" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="10.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="48.140625" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.140625" style="9" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.5703125" style="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="3">
+      <c r="C2" s="5">
         <v>105460</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="5"/>
-      <c r="F2" s="7">
+      <c r="E2" s="7"/>
+      <c r="F2" s="8">
         <v>24.99</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3" s="5">
         <v>105461</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="5"/>
-      <c r="F3" s="7">
+      <c r="E3" s="7"/>
+      <c r="F3" s="8">
         <v>33.99</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="5">
         <v>239334</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="5"/>
-      <c r="F4" s="7">
+      <c r="E4" s="7"/>
+      <c r="F4" s="8">
         <v>29.99</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5" s="5">
         <v>105451</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="5"/>
-      <c r="F5" s="7">
+      <c r="E5" s="7"/>
+      <c r="F5" s="8">
         <v>39.99</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C6" s="5">
         <v>105474</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E6" s="5"/>
-      <c r="F6" s="7">
+      <c r="E6" s="7"/>
+      <c r="F6" s="8">
         <v>34.99</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="3">
+      <c r="C7" s="5">
         <v>107260</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E7" s="5"/>
-      <c r="F7" s="7">
+      <c r="E7" s="7"/>
+      <c r="F7" s="8">
         <v>32.99</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="3">
+      <c r="C8" s="5">
         <v>231292</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E8" s="5"/>
-      <c r="F8" s="7">
+      <c r="E8" s="7"/>
+      <c r="F8" s="8">
         <v>28.99</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="3">
+      <c r="C9" s="5">
         <v>105452</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E9" s="5"/>
-      <c r="F9" s="7">
+      <c r="E9" s="7"/>
+      <c r="F9" s="8">
         <v>38.99</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="3">
+      <c r="C10" s="5">
         <v>106053</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="E10" s="5"/>
-      <c r="F10" s="7">
+      <c r="E10" s="7"/>
+      <c r="F10" s="8">
         <v>17.989999999999998</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="3">
+      <c r="C11" s="5">
         <v>105433</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="E11" s="5"/>
-      <c r="F11" s="7">
+      <c r="E11" s="7"/>
+      <c r="F11" s="8">
         <v>21.99</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C12" s="3">
+      <c r="C12" s="5">
         <v>106050</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="E12" s="5"/>
-      <c r="F12" s="7">
+      <c r="E12" s="7"/>
+      <c r="F12" s="8">
         <v>8.99</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.74803149606299213" right="0.74803149606299213" top="0.98425196850393704" bottom="0.98425196850393704" header="0.51181102362204722" footer="0.51181102362204722"/>
+  <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <headerFooter>
+    <oddHeader>&amp;LGIRO DA PRAÇA - SABADO&amp;C&amp;P - &amp;N</oddHeader>
+  </headerFooter>
 </worksheet>
 </file>
--- a/giro_da_praça_ofertas - SABADO.xlsx
+++ b/giro_da_praça_ofertas - SABADO.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workflow\automacao_giro_ofertas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA4A642D-5B41-4BC6-9126-1CFB9B6EC6C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28E8D7E2-B62B-4C1D-98A4-BE0DD04F24FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="21480" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ofertas Finais" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
@@ -194,7 +194,7 @@
   <numFmts count="1">
     <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -214,24 +214,34 @@
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="9"/>
+      <b/>
+      <sz val="16"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
-      <sz val="9"/>
+      <sz val="16"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
+      <sz val="16"/>
+      <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -242,6 +252,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -272,7 +288,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -280,22 +296,35 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -602,609 +631,609 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F36"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="42" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="25.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="46.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="4.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.7109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="25.28515625" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="32.140625" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="10.7109375" style="12" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="78.42578125" style="12" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.140625" style="12" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.5703125" style="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="3">
+      <c r="C2" s="5">
         <v>100038</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="5"/>
-      <c r="F2" s="7">
+      <c r="E2" s="7"/>
+      <c r="F2" s="8">
         <v>24.69</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="5">
         <v>120994</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="5"/>
-      <c r="F4" s="7">
+      <c r="E4" s="10"/>
+      <c r="F4" s="11">
         <v>9.99</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5" s="5">
         <v>284044</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="5"/>
-      <c r="F5" s="7">
+      <c r="E5" s="10"/>
+      <c r="F5" s="11">
         <v>23.19</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C6" s="5">
         <v>276943</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="E6" s="5"/>
-      <c r="F6" s="7">
+      <c r="E6" s="10"/>
+      <c r="F6" s="11">
         <v>15.59</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="3">
+      <c r="C7" s="5">
         <v>158733</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="E7" s="5"/>
-      <c r="F7" s="7">
+      <c r="E7" s="10"/>
+      <c r="F7" s="11">
         <v>12.29</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="3">
+      <c r="C8" s="5">
         <v>152148</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="E8" s="5"/>
-      <c r="F8" s="7">
+      <c r="E8" s="10"/>
+      <c r="F8" s="11">
         <v>75.489999999999995</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="3">
+      <c r="C9" s="5">
         <v>220822</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="E9" s="5"/>
-      <c r="F9" s="7">
+      <c r="E9" s="10"/>
+      <c r="F9" s="11">
         <v>14.99</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>20</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="3">
+      <c r="C11" s="5">
         <v>302070</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E11" s="5"/>
-      <c r="F11" s="7">
+      <c r="E11" s="7"/>
+      <c r="F11" s="8">
         <v>8.59</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>20</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C12" s="3">
+      <c r="C12" s="5">
         <v>286325</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="E12" s="5"/>
-      <c r="F12" s="7">
+      <c r="E12" s="7"/>
+      <c r="F12" s="8">
         <v>18.89</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>20</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C13" s="3">
+      <c r="C13" s="5">
         <v>345589</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E13" s="5"/>
-      <c r="F13" s="7">
+      <c r="E13" s="7"/>
+      <c r="F13" s="8">
         <v>3.39</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>20</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C14" s="3">
+      <c r="C14" s="5">
         <v>267604</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="E14" s="5"/>
-      <c r="F14" s="7">
+      <c r="E14" s="7"/>
+      <c r="F14" s="8">
         <v>6.19</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>20</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="3">
+      <c r="C15" s="5">
         <v>322187</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="E15" s="5"/>
-      <c r="F15" s="7">
+      <c r="E15" s="7"/>
+      <c r="F15" s="8">
         <v>3.99</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>20</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C16" s="3">
+      <c r="C16" s="5">
         <v>262730</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="E16" s="5"/>
-      <c r="F16" s="7">
+      <c r="E16" s="7"/>
+      <c r="F16" s="8">
         <v>209.99</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C18" s="3">
+      <c r="C18" s="5">
         <v>345608</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="D18" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="E18" s="5"/>
-      <c r="F18" s="7">
+      <c r="E18" s="7"/>
+      <c r="F18" s="8">
         <v>21.19</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C19" s="3">
+      <c r="C19" s="5">
         <v>108856</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="D19" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="E19" s="5"/>
-      <c r="F19" s="7">
+      <c r="E19" s="7"/>
+      <c r="F19" s="8">
         <v>23.89</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C20" s="3">
+      <c r="C20" s="5">
         <v>343895</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D20" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="E20" s="5"/>
-      <c r="F20" s="7">
+      <c r="E20" s="7"/>
+      <c r="F20" s="8">
         <v>10.199999999999999</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C21" s="3">
+      <c r="C21" s="5">
         <v>108771</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="D21" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E21" s="5"/>
-      <c r="F21" s="7">
+      <c r="E21" s="7"/>
+      <c r="F21" s="8">
         <v>17.190000000000001</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>36</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C22" s="3">
+      <c r="C22" s="5">
         <v>105468</v>
       </c>
-      <c r="D22" s="4" t="s">
+      <c r="D22" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="E22" s="5"/>
-      <c r="F22" s="7">
+      <c r="E22" s="7"/>
+      <c r="F22" s="8">
         <v>21.99</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>36</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C23" s="3">
+      <c r="C23" s="5">
         <v>105451</v>
       </c>
-      <c r="D23" s="4" t="s">
+      <c r="D23" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="E23" s="5"/>
-      <c r="F23" s="7">
+      <c r="E23" s="7"/>
+      <c r="F23" s="8">
         <v>41.99</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>36</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C24" s="3">
+      <c r="C24" s="5">
         <v>105474</v>
       </c>
-      <c r="D24" s="4" t="s">
+      <c r="D24" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="E24" s="5"/>
-      <c r="F24" s="7">
+      <c r="E24" s="7"/>
+      <c r="F24" s="8">
         <v>37.99</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>36</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C25" s="3">
+      <c r="C25" s="5">
         <v>107260</v>
       </c>
-      <c r="D25" s="4" t="s">
+      <c r="D25" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="E25" s="5"/>
-      <c r="F25" s="7">
+      <c r="E25" s="7"/>
+      <c r="F25" s="8">
         <v>34.99</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>36</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C26" s="3">
+      <c r="C26" s="5">
         <v>105433</v>
       </c>
-      <c r="D26" s="4" t="s">
+      <c r="D26" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="E26" s="5"/>
-      <c r="F26" s="7">
+      <c r="E26" s="7"/>
+      <c r="F26" s="8">
         <v>25.99</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>36</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C27" s="3">
+      <c r="C27" s="5">
         <v>106034</v>
       </c>
-      <c r="D27" s="4" t="s">
+      <c r="D27" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="E27" s="5"/>
-      <c r="F27" s="7">
+      <c r="E27" s="7"/>
+      <c r="F27" s="8">
         <v>9.99</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C28" s="3">
+      <c r="C28" s="5">
         <v>291439</v>
       </c>
-      <c r="D28" s="4" t="s">
+      <c r="D28" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="E28" s="5"/>
-      <c r="F28" s="7">
+      <c r="E28" s="7"/>
+      <c r="F28" s="8">
         <v>10.79</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>36</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C29" s="3">
+      <c r="C29" s="5">
         <v>305039</v>
       </c>
-      <c r="D29" s="4" t="s">
+      <c r="D29" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="E29" s="5"/>
-      <c r="F29" s="7">
+      <c r="E29" s="7"/>
+      <c r="F29" s="8">
         <v>18.989999999999998</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C30" s="3">
+      <c r="C30" s="5">
         <v>329704</v>
       </c>
-      <c r="D30" s="4" t="s">
+      <c r="D30" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="E30" s="5"/>
-      <c r="F30" s="7">
+      <c r="E30" s="7"/>
+      <c r="F30" s="8">
         <v>29.49</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C31" s="3">
+      <c r="C31" s="5">
         <v>329696</v>
       </c>
-      <c r="D31" s="4" t="s">
+      <c r="D31" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="E31" s="5"/>
-      <c r="F31" s="7">
+      <c r="E31" s="7"/>
+      <c r="F31" s="8">
         <v>30.99</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C32" s="3">
+      <c r="C32" s="5">
         <v>343563</v>
       </c>
-      <c r="D32" s="4" t="s">
+      <c r="D32" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="E32" s="5"/>
-      <c r="F32" s="7">
+      <c r="E32" s="7"/>
+      <c r="F32" s="8">
         <v>36.19</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C33" s="3">
+      <c r="C33" s="5">
         <v>343562</v>
       </c>
-      <c r="D33" s="4" t="s">
+      <c r="D33" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="E33" s="5"/>
-      <c r="F33" s="7">
+      <c r="E33" s="7"/>
+      <c r="F33" s="8">
         <v>44.19</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C34" s="3">
+      <c r="C34" s="5">
         <v>292399</v>
       </c>
-      <c r="D34" s="4" t="s">
+      <c r="D34" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="E34" s="5"/>
-      <c r="F34" s="7">
+      <c r="E34" s="7"/>
+      <c r="F34" s="8">
         <v>9.99</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C35" s="3">
+      <c r="C35" s="5">
         <v>301962</v>
       </c>
-      <c r="D35" s="4" t="s">
+      <c r="D35" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="E35" s="5"/>
-      <c r="F35" s="7">
+      <c r="E35" s="7"/>
+      <c r="F35" s="8">
         <v>15.89</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C36" s="3">
+      <c r="C36" s="5">
         <v>335536</v>
       </c>
-      <c r="D36" s="4" t="s">
+      <c r="D36" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="E36" s="5"/>
-      <c r="F36" s="7">
+      <c r="E36" s="7"/>
+      <c r="F36" s="8">
         <v>28.29</v>
       </c>
     </row>

--- a/giro_da_praça_ofertas - SABADO.xlsx
+++ b/giro_da_praça_ofertas - SABADO.xlsx
@@ -8,19 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workflow\automacao_giro_ofertas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7008BCDA-3212-485F-A20D-626F662E11DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42B03D59-B86F-49A9-9E72-8EBBF493835F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="21480" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ofertas Finais" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="96">
   <si>
     <t>NOME_PROMOÇÃO</t>
   </si>
@@ -167,6 +167,147 @@
   </si>
   <si>
     <t>TIRINHAS DE TILÁPIA COSTA SUL 300G EMPANADO</t>
+  </si>
+  <si>
+    <t>SEXTA E SABADO - HORTIFRUTI 21 E 22/08/26</t>
+  </si>
+  <si>
+    <t>#04 HORTIFRUTI - FRUTAS</t>
+  </si>
+  <si>
+    <t>ABACATE KG</t>
+  </si>
+  <si>
+    <t>ABACAXI UN</t>
+  </si>
+  <si>
+    <t>AMEIXA KG</t>
+  </si>
+  <si>
+    <t>KIWI KG</t>
+  </si>
+  <si>
+    <t>LARANJA KG</t>
+  </si>
+  <si>
+    <t>LIMÃO TAITI KG</t>
+  </si>
+  <si>
+    <t>MANGA KG PALMER</t>
+  </si>
+  <si>
+    <t>MANGA KG TOMY</t>
+  </si>
+  <si>
+    <t>MELÃO AMARELO KG REI | REDINHA</t>
+  </si>
+  <si>
+    <t>MEXERICA VERONA KG</t>
+  </si>
+  <si>
+    <t>MORANGO RM OLIVEIRA BDJ 250G</t>
+  </si>
+  <si>
+    <t>UVA VITORIA MARIM BDJ 500G</t>
+  </si>
+  <si>
+    <t>#04 HORTIFRUTI - LEGUMES E TUBÉRCULOS</t>
+  </si>
+  <si>
+    <t>BATATA DOCE BRANCA KG</t>
+  </si>
+  <si>
+    <t>CARÁ KG</t>
+  </si>
+  <si>
+    <t>CENOURA KG</t>
+  </si>
+  <si>
+    <t>INHAME KG</t>
+  </si>
+  <si>
+    <t>TOMATE CARMEM KG</t>
+  </si>
+  <si>
+    <t>#04 HORTIFRUTI - TEMPEROS FRESCOS</t>
+  </si>
+  <si>
+    <t>CEBOLA NACIONAL KG</t>
+  </si>
+  <si>
+    <t>BIRITAO - SABADO</t>
+  </si>
+  <si>
+    <t>#05 BEBIDA - #00 BEBIDAS GASEIFICADAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ICE SMIRNOFF LONG NECK 275ML </t>
+  </si>
+  <si>
+    <t>REFRIGERANTE H2OH 1,5L LIMONETO</t>
+  </si>
+  <si>
+    <t>SKOL BEATS SENSES 269ML</t>
+  </si>
+  <si>
+    <t>#05 BEBIDA - CERVEJAS</t>
+  </si>
+  <si>
+    <t>CERVEJA HEINEKEN 330ML</t>
+  </si>
+  <si>
+    <t>CERVEJA HEINEKEN 600ML</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CERVEJA MICHELOB ULTRA LONG NECK 330ML </t>
+  </si>
+  <si>
+    <t>#05 BEBIDA - CERVEJAS CX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CERVEJA AMSTEL LAGER 12 X 269ML </t>
+  </si>
+  <si>
+    <t>CERVEJA ANTARCTICA 15 X 269ML MULTIPACK</t>
+  </si>
+  <si>
+    <t>CERVEJA HEINEKEN SLEECK 12 X 350ML</t>
+  </si>
+  <si>
+    <t>#05 BEBIDA - DESTILADOS</t>
+  </si>
+  <si>
+    <t>BEBIDA ALCOOLICA FIU FIU 750ML TANGERINA ACEROLA</t>
+  </si>
+  <si>
+    <t>CACHAÇA BANANAZINHA 900ML</t>
+  </si>
+  <si>
+    <t>CACHAÇA VELHO BARREIRO 910ML CAFÉ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CACHAÇA YPIOCA 965ML OURO COM PALHA </t>
+  </si>
+  <si>
+    <t>VODKA SKYY 980ML</t>
+  </si>
+  <si>
+    <t>WHISKY BLACK &amp; WHITE 1L 8 ANOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WHISKY BUCHANANS 1L 12 ANOS </t>
+  </si>
+  <si>
+    <t>WHISKY CHIVAS REGAL 1L 12 ANOS</t>
+  </si>
+  <si>
+    <t>#05 BEBIDA - FERMENTADOS</t>
+  </si>
+  <si>
+    <t>CHOPP DE VINHO STEMPEL 600ML PINK</t>
+  </si>
+  <si>
+    <t>VINHO PERGOLA 1L TINTO SUAVE</t>
   </si>
 </sst>
 </file>
@@ -176,7 +317,7 @@
   <numFmts count="1">
     <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -196,21 +337,31 @@
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="9"/>
+      <b/>
+      <sz val="16"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
-      <sz val="9"/>
+      <sz val="16"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
+      <sz val="16"/>
+      <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -254,7 +405,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -262,22 +413,26 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -580,578 +735,1254 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F32"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F71"/>
+  <sheetFormatPr defaultRowHeight="43.5" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="30.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="37.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="54" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="4.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.7109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.42578125" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="37.5703125" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="10.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="91.28515625" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.140625" style="9" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.5703125" style="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="3">
+      <c r="C2" s="5">
         <v>286632</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="5"/>
-      <c r="F2" s="7">
+      <c r="E2" s="7"/>
+      <c r="F2" s="8">
         <v>21.99</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3" s="5">
         <v>201117</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="5"/>
-      <c r="F3" s="7">
+      <c r="E3" s="7"/>
+      <c r="F3" s="8">
         <v>17.989999999999998</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="5">
         <v>266094</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="5"/>
-      <c r="F4" s="7">
+      <c r="E4" s="7"/>
+      <c r="F4" s="8">
         <v>13.99</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5" s="5">
         <v>156502</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="5"/>
-      <c r="F5" s="7">
+      <c r="E5" s="7"/>
+      <c r="F5" s="8">
         <v>44.99</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C6" s="5">
         <v>142756</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E6" s="5"/>
-      <c r="F6" s="7">
+      <c r="E6" s="7"/>
+      <c r="F6" s="8">
         <v>9.99</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="3">
+      <c r="C7" s="5">
         <v>338923</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="E7" s="5"/>
-      <c r="F7" s="7">
+      <c r="E7" s="7"/>
+      <c r="F7" s="8">
         <v>10.99</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="3">
+      <c r="C9" s="5">
         <v>345608</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="E9" s="5"/>
-      <c r="F9" s="7">
+      <c r="E9" s="7"/>
+      <c r="F9" s="8">
         <v>22.99</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="3">
+      <c r="C10" s="5">
         <v>173075</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="E10" s="5"/>
-      <c r="F10" s="7">
+      <c r="E10" s="7"/>
+      <c r="F10" s="8">
         <v>25.99</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="3">
+      <c r="C11" s="5">
         <v>190327</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="E11" s="5"/>
-      <c r="F11" s="7">
+      <c r="E11" s="7"/>
+      <c r="F11" s="8">
         <v>20.99</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C12" s="3">
+      <c r="C12" s="5">
         <v>108770</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="E12" s="5"/>
-      <c r="F12" s="7">
+      <c r="E12" s="7"/>
+      <c r="F12" s="8">
         <v>25.99</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C13" s="3">
+      <c r="C13" s="5">
         <v>109388</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E13" s="5"/>
-      <c r="F13" s="7">
+      <c r="E13" s="7"/>
+      <c r="F13" s="8">
         <v>18.989999999999998</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C14" s="3">
+      <c r="C14" s="5">
         <v>108788</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="E14" s="5"/>
-      <c r="F14" s="7">
+      <c r="E14" s="7"/>
+      <c r="F14" s="8">
         <v>21.99</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C15" s="3">
+      <c r="C15" s="5">
         <v>171237</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="E15" s="5"/>
-      <c r="F15" s="7">
+      <c r="E15" s="7"/>
+      <c r="F15" s="8">
         <v>24.99</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>25</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="3">
+      <c r="C16" s="5">
         <v>105450</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="E16" s="5"/>
-      <c r="F16" s="7">
+      <c r="E16" s="7"/>
+      <c r="F16" s="8">
         <v>46.99</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>25</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C17" s="3">
+      <c r="C17" s="5">
         <v>105468</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D17" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="E17" s="5"/>
-      <c r="F17" s="7">
+      <c r="E17" s="7"/>
+      <c r="F17" s="8">
         <v>21.99</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>25</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C18" s="3">
+      <c r="C18" s="5">
         <v>105451</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="D18" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="E18" s="5"/>
-      <c r="F18" s="7">
+      <c r="E18" s="7"/>
+      <c r="F18" s="8">
         <v>42.99</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>25</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C19" s="3">
+      <c r="C19" s="5">
         <v>105471</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="D19" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="E19" s="5"/>
-      <c r="F19" s="7">
+      <c r="E19" s="7"/>
+      <c r="F19" s="8">
         <v>22.99</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>25</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C20" s="3">
+      <c r="C20" s="5">
         <v>107260</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D20" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="E20" s="5"/>
-      <c r="F20" s="7">
+      <c r="E20" s="7"/>
+      <c r="F20" s="8">
         <v>36.99</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>25</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C21" s="3">
+      <c r="C21" s="5">
         <v>298422</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="D21" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="E21" s="5"/>
-      <c r="F21" s="7">
+      <c r="E21" s="7"/>
+      <c r="F21" s="8">
         <v>23.99</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>25</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C22" s="3">
+      <c r="C22" s="5">
         <v>106053</v>
       </c>
-      <c r="D22" s="4" t="s">
+      <c r="D22" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="E22" s="5"/>
-      <c r="F22" s="7">
+      <c r="E22" s="7"/>
+      <c r="F22" s="8">
         <v>19.989999999999998</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C23" s="3">
+      <c r="C23" s="5">
         <v>341509</v>
       </c>
-      <c r="D23" s="4" t="s">
+      <c r="D23" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E23" s="5"/>
-      <c r="F23" s="7">
+      <c r="E23" s="7"/>
+      <c r="F23" s="8">
         <v>31.99</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C24" s="3">
+      <c r="C24" s="5">
         <v>209691</v>
       </c>
-      <c r="D24" s="4" t="s">
+      <c r="D24" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="E24" s="5"/>
-      <c r="F24" s="7">
+      <c r="E24" s="7"/>
+      <c r="F24" s="8">
         <v>35.99</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C25" s="3">
+      <c r="C25" s="5">
         <v>204452</v>
       </c>
-      <c r="D25" s="4" t="s">
+      <c r="D25" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="E25" s="5"/>
-      <c r="F25" s="7">
+      <c r="E25" s="7"/>
+      <c r="F25" s="8">
         <v>23.79</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C26" s="3">
+      <c r="C26" s="5">
         <v>323487</v>
       </c>
-      <c r="D26" s="4" t="s">
+      <c r="D26" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="E26" s="5"/>
-      <c r="F26" s="7">
+      <c r="E26" s="7"/>
+      <c r="F26" s="8">
         <v>47.99</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C27" s="3">
+      <c r="C27" s="5">
         <v>289126</v>
       </c>
-      <c r="D27" s="4" t="s">
+      <c r="D27" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="E27" s="5"/>
-      <c r="F27" s="7">
+      <c r="E27" s="7"/>
+      <c r="F27" s="8">
         <v>7.99</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C28" s="3">
+      <c r="C28" s="5">
         <v>292399</v>
       </c>
-      <c r="D28" s="4" t="s">
+      <c r="D28" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="E28" s="5"/>
-      <c r="F28" s="7">
+      <c r="E28" s="7"/>
+      <c r="F28" s="8">
         <v>10.99</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C29" s="3">
+      <c r="C29" s="5">
         <v>301962</v>
       </c>
-      <c r="D29" s="4" t="s">
+      <c r="D29" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="E29" s="5"/>
-      <c r="F29" s="7">
+      <c r="E29" s="7"/>
+      <c r="F29" s="8">
         <v>15.99</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C30" s="3">
+      <c r="C30" s="5">
         <v>295464</v>
       </c>
-      <c r="D30" s="4" t="s">
+      <c r="D30" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="E30" s="5"/>
-      <c r="F30" s="7">
+      <c r="E30" s="7"/>
+      <c r="F30" s="8">
         <v>25.99</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C31" s="3">
+      <c r="C31" s="5">
         <v>170464</v>
       </c>
-      <c r="D31" s="4" t="s">
+      <c r="D31" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="E31" s="5"/>
-      <c r="F31" s="7">
+      <c r="E31" s="7"/>
+      <c r="F31" s="8">
         <v>2.19</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C32" s="3">
+      <c r="C32" s="5">
         <v>284246</v>
       </c>
-      <c r="D32" s="4" t="s">
+      <c r="D32" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="E32" s="5"/>
-      <c r="F32" s="7">
+      <c r="E32" s="7"/>
+      <c r="F32" s="8">
         <v>12.99</v>
       </c>
     </row>
+    <row r="34" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C34" s="5">
+        <v>104864</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="E34" s="7"/>
+      <c r="F34" s="8">
+        <v>5.19</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C35" s="5">
+        <v>104848</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="E35" s="7"/>
+      <c r="F35" s="8">
+        <v>6.29</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C36" s="5">
+        <v>104866</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E36" s="7"/>
+      <c r="F36" s="8">
+        <v>24.99</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C37" s="5">
+        <v>109641</v>
+      </c>
+      <c r="D37" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="E37" s="7"/>
+      <c r="F37" s="8">
+        <v>38.99</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C38" s="5">
+        <v>104931</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="E38" s="7"/>
+      <c r="F38" s="8">
+        <v>6.99</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C39" s="5">
+        <v>104855</v>
+      </c>
+      <c r="D39" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="E39" s="7"/>
+      <c r="F39" s="8">
+        <v>10.69</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C40" s="5">
+        <v>104928</v>
+      </c>
+      <c r="D40" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="E40" s="7"/>
+      <c r="F40" s="8">
+        <v>9.59</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C41" s="5">
+        <v>104883</v>
+      </c>
+      <c r="D41" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="E41" s="7"/>
+      <c r="F41" s="8">
+        <v>9.59</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C42" s="5">
+        <v>113290</v>
+      </c>
+      <c r="D42" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="E42" s="7"/>
+      <c r="F42" s="8">
+        <v>15.39</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C43" s="5">
+        <v>104926</v>
+      </c>
+      <c r="D43" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="E43" s="7"/>
+      <c r="F43" s="8">
+        <v>17.989999999999998</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C44" s="5">
+        <v>227687</v>
+      </c>
+      <c r="D44" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="E44" s="7"/>
+      <c r="F44" s="8">
+        <v>17.989999999999998</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C45" s="5">
+        <v>223397</v>
+      </c>
+      <c r="D45" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="E45" s="7"/>
+      <c r="F45" s="8">
+        <v>10.99</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C46" s="5">
+        <v>104893</v>
+      </c>
+      <c r="D46" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="E46" s="7"/>
+      <c r="F46" s="8">
+        <v>11.99</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C47" s="5">
+        <v>104891</v>
+      </c>
+      <c r="D47" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="E47" s="7"/>
+      <c r="F47" s="8">
+        <v>9.69</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C48" s="5">
+        <v>104862</v>
+      </c>
+      <c r="D48" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="E48" s="7"/>
+      <c r="F48" s="8">
+        <v>7.59</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C49" s="5">
+        <v>104953</v>
+      </c>
+      <c r="D49" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="E49" s="7"/>
+      <c r="F49" s="8">
+        <v>8.99</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C50" s="5">
+        <v>104961</v>
+      </c>
+      <c r="D50" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="E50" s="7"/>
+      <c r="F50" s="8">
+        <v>6.99</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C51" s="5">
+        <v>104919</v>
+      </c>
+      <c r="D51" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="E51" s="7"/>
+      <c r="F51" s="8">
+        <v>6.89</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C53" s="5">
+        <v>102278</v>
+      </c>
+      <c r="D53" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="E53" s="7"/>
+      <c r="F53" s="8">
+        <v>8.99</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C54" s="5">
+        <v>325127</v>
+      </c>
+      <c r="D54" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="E54" s="7"/>
+      <c r="F54" s="8">
+        <v>8.19</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C55" s="5">
+        <v>260019</v>
+      </c>
+      <c r="D55" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="E55" s="7"/>
+      <c r="F55" s="8">
+        <v>7.99</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C56" s="5">
+        <v>108423</v>
+      </c>
+      <c r="D56" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="E56" s="7"/>
+      <c r="F56" s="8">
+        <v>6.99</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C57" s="5">
+        <v>157496</v>
+      </c>
+      <c r="D57" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="E57" s="7"/>
+      <c r="F57" s="8">
+        <v>14.99</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C58" s="5">
+        <v>263389</v>
+      </c>
+      <c r="D58" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="E58" s="7"/>
+      <c r="F58" s="8">
+        <v>6.69</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C59" s="5">
+        <v>239446</v>
+      </c>
+      <c r="D59" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="E59" s="7"/>
+      <c r="F59" s="8">
+        <f>12*3.19</f>
+        <v>38.28</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C60" s="5">
+        <v>341231</v>
+      </c>
+      <c r="D60" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="E60" s="7"/>
+      <c r="F60" s="8">
+        <f>15*2.89</f>
+        <v>43.35</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C61" s="5">
+        <v>303282</v>
+      </c>
+      <c r="D61" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="E61" s="7"/>
+      <c r="F61" s="8">
+        <f>12*5.59</f>
+        <v>67.08</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C62" s="5">
+        <v>236673</v>
+      </c>
+      <c r="D62" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="E62" s="7"/>
+      <c r="F62" s="8">
+        <v>41.99</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C63" s="5">
+        <v>215568</v>
+      </c>
+      <c r="D63" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="E63" s="7"/>
+      <c r="F63" s="8">
+        <v>34.99</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C64" s="5">
+        <v>207308</v>
+      </c>
+      <c r="D64" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="E64" s="7"/>
+      <c r="F64" s="8">
+        <v>37.99</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C65" s="5">
+        <v>157984</v>
+      </c>
+      <c r="D65" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="E65" s="7"/>
+      <c r="F65" s="8">
+        <v>59.99</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C66" s="5">
+        <v>134156</v>
+      </c>
+      <c r="D66" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="E66" s="7"/>
+      <c r="F66" s="8">
+        <v>51.99</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C67" s="5">
+        <v>110373</v>
+      </c>
+      <c r="D67" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="E67" s="7"/>
+      <c r="F67" s="8">
+        <v>136.99</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C68" s="5">
+        <v>109726</v>
+      </c>
+      <c r="D68" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="E68" s="7"/>
+      <c r="F68" s="8">
+        <v>229.99</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C69" s="5">
+        <v>109727</v>
+      </c>
+      <c r="D69" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="E69" s="7"/>
+      <c r="F69" s="8">
+        <v>149.99</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C70" s="5">
+        <v>300690</v>
+      </c>
+      <c r="D70" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="E70" s="7"/>
+      <c r="F70" s="8">
+        <v>11.99</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C71" s="5">
+        <v>139964</v>
+      </c>
+      <c r="D71" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="E71" s="7"/>
+      <c r="F71" s="8">
+        <v>34.99</v>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.74803149606299213" right="0.74803149606299213" top="0.98425196850393704" bottom="0.98425196850393704" header="0.51181102362204722" footer="0.51181102362204722"/>
+  <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <headerFooter>
+    <oddHeader>&amp;LGIRO DA PRAÇA - SABADO&amp;C&amp;P - &amp;N</oddHeader>
+  </headerFooter>
 </worksheet>
 </file>